--- a/personal.xlsx
+++ b/personal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1A\estadisticas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE2647CD-2D55-42BF-9F9A-E0FB4DF57423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B0EEC7-0DA3-4BF3-B7E8-472ED289A641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D2DA9B68-23D1-4187-8AE6-056FF12B504C}"/>
   </bookViews>
@@ -118,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,6 +131,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -261,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -281,6 +287,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F40F94-EA63-44B7-9AF3-634675B3C45E}">
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -690,7 +697,7 @@
         <v>22545889</v>
       </c>
       <c r="E8" s="9">
-        <f t="shared" ref="E8:F8" si="0">(E6+E7)</f>
+        <f t="shared" ref="E8" si="0">(E6+E7)</f>
         <v>20160</v>
       </c>
       <c r="F8" s="9">
@@ -783,15 +790,15 @@
         <v>288.88749999999999</v>
       </c>
       <c r="G13" s="9">
-        <v>20</v>
+        <v>20000</v>
       </c>
       <c r="H13" s="10">
         <f>E13-G13</f>
-        <v>30220</v>
+        <v>10240</v>
       </c>
       <c r="I13" s="16">
         <f>F13*H13</f>
-        <v>8730180.25</v>
+        <v>2958208</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
@@ -897,6 +904,12 @@
         <v>18900170</v>
       </c>
     </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="19">
+        <f>I8+I13+I19</f>
+        <v>33220790.313492063</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/personal.xlsx
+++ b/personal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1A\estadisticas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B0EEC7-0DA3-4BF3-B7E8-472ED289A641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA98A981-BC26-495A-9CA7-DBCA2ECA1B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D2DA9B68-23D1-4187-8AE6-056FF12B504C}"/>
   </bookViews>
